--- a/docs/compliance/IFRS9_Impairment_Compliance_Audit.xlsx
+++ b/docs/compliance/IFRS9_Impairment_Compliance_Audit.xlsx
@@ -2115,27 +2115,27 @@
       </c>
       <c r="C5" s="22" t="inlineStr">
         <is>
-          <t>The PD engine has not run on the clean install</t>
+          <t>The PD and LGD of the clean install are the bootstrap's, not MAIIC's</t>
         </is>
       </c>
       <c r="D5" s="22" t="inlineStr">
         <is>
-          <t>The transition-matrix PD runs from its screen and is not yet callable by the bootstrap; every PD is null and the ECL of the period is nil.</t>
+          <t>PdEngineService and LgdEngineService run the transition matrix and the cohort workout under the bootstrap label; no MAIIC reviewer has key-locked a matrix or an LGD calculation in the system.</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
         <is>
-          <t>No weighted ECL for a period; the scenario sensitivity reports zero loans with a PD.</t>
+          <t>The ECL of 8.33bn at August 2026 is a system figure awaiting review.</t>
         </is>
       </c>
       <c r="F5" s="22" t="inlineStr">
         <is>
-          <t>Lift the transition-matrix logic into a service the bootstrap calls (engine step 4), then run the ECL under the approved scenario set.</t>
+          <t>A reviewer key-locks the matrix and the LGD on their screens; the ECL is then re-run under the approved scenario set.</t>
         </is>
       </c>
       <c r="G5" s="22" t="inlineStr">
         <is>
-          <t>Dupleix</t>
+          <t>Dr Thom / the reviewer</t>
         </is>
       </c>
       <c r="H5" s="22" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-08 20:26:01 from maiic_ifrs9_bootstrap. The PASS/FAIL in column E is a formula on columns B and C, so it recomputes if a figure is typed over.</t>
+          <t>Generated 2026-10-08 20:35:55 from maiic_ifrs9_bootstrap. The PASS/FAIL in column E is a formula on columns B and C, so it recomputes if a figure is typed over.</t>
         </is>
       </c>
     </row>

--- a/docs/compliance/IFRS9_Impairment_Compliance_Audit.xlsx
+++ b/docs/compliance/IFRS9_Impairment_Compliance_Audit.xlsx
@@ -2279,7 +2279,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-08 20:35:55 from maiic_ifrs9_bootstrap. The PASS/FAIL in column E is a formula on columns B and C, so it recomputes if a figure is typed over.</t>
+          <t>Generated 2026-10-08 20:53:34 from maiic_ifrs9_bootstrap. The PASS/FAIL in column E is a formula on columns B and C, so it recomputes if a figure is typed over.</t>
         </is>
       </c>
     </row>

--- a/docs/compliance/IFRS9_Impairment_Compliance_Audit.xlsx
+++ b/docs/compliance/IFRS9_Impairment_Compliance_Audit.xlsx
@@ -2279,7 +2279,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-08 20:53:34 from maiic_ifrs9_bootstrap. The PASS/FAIL in column E is a formula on columns B and C, so it recomputes if a figure is typed over.</t>
+          <t>Generated 2026-10-08 21:18:14 from maiic_ifrs9_bootstrap. The PASS/FAIL in column E is a formula on columns B and C, so it recomputes if a figure is typed over.</t>
         </is>
       </c>
     </row>

--- a/docs/compliance/IFRS9_Impairment_Compliance_Audit.xlsx
+++ b/docs/compliance/IFRS9_Impairment_Compliance_Audit.xlsx
@@ -1728,7 +1728,7 @@
       </c>
       <c r="H15" s="22" t="inlineStr">
         <is>
-          <t>Financial Modelling, Forward-Looking Model: /regression; fli:correlate; fli:method-cards (fli:method-cards; /fli/transmission-methods)</t>
+          <t>Financial Modelling, Forward-Looking Model: /regression; fli:correlate; fli:method-cards; Governance Centre, the cards inline on the setting: /eir-governance; fli:method-cards</t>
         </is>
       </c>
       <c r="I15" s="22" t="inlineStr"/>
@@ -1971,7 +1971,7 @@
       </c>
       <c r="H22" s="22" t="inlineStr">
         <is>
-          <t>Governance Centre: /eir-governance; Data Foundation, Loan Book (2025-11)</t>
+          <t>Financial Modelling, Mega Farm Programme: /megafarm; Governance Centre: /eir-governance</t>
         </is>
       </c>
       <c r="I22" s="22" t="inlineStr"/>
@@ -2279,7 +2279,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-08 21:18:14 from maiic_ifrs9_bootstrap. The PASS/FAIL in column E is a formula on columns B and C, so it recomputes if a figure is typed over.</t>
+          <t>Generated 2026-10-08 21:40:05 from maiic_ifrs9_bootstrap. The PASS/FAIL in column E is a formula on columns B and C, so it recomputes if a figure is typed over.</t>
         </is>
       </c>
     </row>

--- a/docs/compliance/IFRS9_Impairment_Compliance_Audit.xlsx
+++ b/docs/compliance/IFRS9_Impairment_Compliance_Audit.xlsx
@@ -2279,7 +2279,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-08 21:40:05 from maiic_ifrs9_bootstrap. The PASS/FAIL in column E is a formula on columns B and C, so it recomputes if a figure is typed over.</t>
+          <t>Generated 2026-10-09 00:03:13 from maiic_ifrs9_bootstrap. The PASS/FAIL in column E is a formula on columns B and C, so it recomputes if a figure is typed over.</t>
         </is>
       </c>
     </row>

--- a/docs/compliance/IFRS9_Impairment_Compliance_Audit.xlsx
+++ b/docs/compliance/IFRS9_Impairment_Compliance_Audit.xlsx
@@ -969,7 +969,7 @@
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
         <is>
-          <t>B5.5.28 to B5.5.30</t>
+          <t>B5.5.1 to B5.5.6, B5.5.28 to B5.5.30</t>
         </is>
       </c>
       <c r="B25" s="17" t="inlineStr">
@@ -990,7 +990,7 @@
     <row r="26">
       <c r="A26" s="16" t="inlineStr">
         <is>
-          <t>B5.5.33 to B5.5.35</t>
+          <t>B5.5.55</t>
         </is>
       </c>
       <c r="B26" s="17" t="inlineStr">
@@ -1102,7 +1102,7 @@
     <row r="35">
       <c r="A35" s="19" t="inlineStr">
         <is>
-          <t>Source: IFRS 9 Financial Instruments as issued by the IASB, section 5.5 and B5.5.1 to B5.5.55. The Reserve Bank of Malawi Financial Services (Credit Risk Management for Development Finance Institutions) Directive 2018 (docs/regulatory). Specification: docs/MAIIC_EIR_Engine_Specification_v4_2026-10-07.md sections 3.6, 13, 14, 15, 16.</t>
+          <t>Source: IFRS 9 Financial Instruments as issued by the IASB, section 5.5 and B5.5.1 to B5.5.55; 5.4.4 and B5.4.9 (write-off). The Reserve Bank of Malawi Financial Services (Credit Risk Management for Development Finance Institutions) Directive 2018 (docs/regulatory). Specification: docs/MAIIC_EIR_Engine_Specification_v4_2026-10-07.md sections 3.6, 13, 14, 15, 16.</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="21" t="inlineStr">
         <is>
-          <t>Malawi Agricultural and Industrial Investment Company (MAIIC) - IFRS 9 EIR and ECL system - build of 8 October 2026 against specification v4. Prepared 8 October 2026 from the build of specification v4: the staged loan books of July 2024 to August 2026 on the clean install, the Governance Centre's staging and forward-looking settings, the forward-looking chain (fli:correlate), the scenario set of 15.8, and the PHPUnit suite. The PD engine (transition matrices) has not run on the clean install, so the ECL figures there are nil; the rows below audit the mechanics and the settings. Reviewer: Dr Thomson Kumwenda (CFO), then Deloitte. Status definitions: see 'Contents'.</t>
+          <t>Malawi Agricultural and Industrial Investment Company (MAIIC) - IFRS 9 EIR and ECL system - build of 14 October 2026 (branch eir_revenue_recognition, commit abe140d) against specification v4. As of 14 October 2026: the code at commit abe140d and the fresh bootstrap maiic_ifrs9_results2 of 13 October 2026 (made before commit 216aee2, so its discounting and Mega Farm figures predate those changes), read with SELECTs only; the Governance Centre's staging and forward-looking settings; the PHPUnit suite as written (not run for this audit). Main book at September 2026 on that bootstrap: 134 loans, gross 23.19bn, ECL 11.57bn undiscounted, 7.12bn discounted on the 62 loans the time-phased engine resolved (72 unresolved). Reviewer: Dr Thomson Kumwenda (CFO), then Deloitte. Status definitions: see 'Contents'.</t>
         </is>
       </c>
     </row>
@@ -1298,25 +1298,29 @@
       </c>
       <c r="E6" s="22" t="inlineStr">
         <is>
-          <t>TimePhasedEclService computes the allowance per loan as EAD x PD x LGD, discounted at the EIR, for the period; ifrs9:recalculate-ecl runs it per portfolio; the bootstrap runs it for the last period.</t>
-        </is>
-      </c>
-      <c r="F6" s="22" t="inlineStr"/>
+          <t>ifrs9:segment-ecl computes the allowance per loan as EAD x PD x LGD on the post-FLI PD for every portfolio of a month and fails closed, naming the loans, when a stage, PD or LGD is missing or a portfolio mixes Mega Farm with MAIIC's own loans; the bootstrap and the month-end (fli:month-end) run it for every period. On the fresh bootstrap the main book carries an allowance in every month (11.57bn undiscounted at September 2026).</t>
+        </is>
+      </c>
+      <c r="F6" s="22" t="inlineStr">
+        <is>
+          <t>Fresh bootstrap maiic_ifrs9_results2 (13 October 2026, before commit 216aee2). Until 14 October 2026 the row said the PD engine must run for a figure.</t>
+        </is>
+      </c>
       <c r="G6" s="22" t="inlineStr">
         <is>
-          <t>Compliant in mechanics; the PD engine must run for a figure.</t>
+          <t>Compliant; the figures are system figures under the bootstrap label, not MAIIC-approved (finding F1).</t>
         </is>
       </c>
       <c r="H6" s="22" t="inlineStr">
         <is>
-          <t>Financial Modelling, ECL Calculation: /expected-credit-loss</t>
+          <t>ECL Processing, ECL Calculation: /expected-credit-loss/list</t>
         </is>
       </c>
       <c r="I6" s="22" t="inlineStr"/>
       <c r="J6" s="22" t="inlineStr"/>
       <c r="K6" s="22" t="inlineStr">
         <is>
-          <t>Tests\Feature\Ecl\TimePhasedEclServiceTest; Tests\Feature\Ecl\EclDiscountRateServiceTest</t>
+          <t>Tests\Feature\Ecl\EclGoldenNumberTest::it_computes_golden_ecl_per_stage_for_prefli_collection_lgd; Tests\Feature\Ecl\TimePhasedEclServiceTest</t>
         </is>
       </c>
     </row>
@@ -1343,7 +1347,7 @@
       </c>
       <c r="E7" s="22" t="inlineStr">
         <is>
-          <t>StagingService stages every period: Stage 2 from 31 days past due in every class (the directive), the SICR flag from the qualitative groups, and the ECL takes the lifetime window for Stage 2.</t>
+          <t>StagingService stages every period: Stage 2 from 31 days past due in every class, the SICR flag from the qualitative groups; the ECL takes the lifetime PD for Stage 2, compounding beyond the 12-month PD. Since 216aee2 the days past due read E-Banker's instalment chart in force at each month-end.</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -1358,7 +1362,7 @@
       </c>
       <c r="H7" s="22" t="inlineStr">
         <is>
-          <t>Governance Centre, Staging &amp; SICR Rules: /stageing-rules; Data Foundation, Loan Book</t>
+          <t>Settings, Staging basis: /setting?tab=staging; IFRS 9 Model Setup, Staging &amp; SICR Rules: /sicr-groups; ECL Processing, ECL Calculation: /expected-credit-loss/list</t>
         </is>
       </c>
       <c r="I7" s="22" t="inlineStr"/>
@@ -1369,7 +1373,7 @@
       </c>
       <c r="K7" s="22" t="inlineStr">
         <is>
-          <t>Tests\Feature\Eir\StagingServiceTest</t>
+          <t>Tests\Feature\Ecl\TimePhasedEclServiceTest::test_a_stage_two_lifetime_compounds_beyond_the_twelve_month_pd; Tests\Feature\Eir\StagingServiceTest::test_the_trigger_reads_the_chart_in_force_at_the_month_end_not_a_later_one</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1390,7 @@
       </c>
       <c r="C8" s="22" t="inlineStr">
         <is>
-          <t>Measure the loss allowance at an amount equal to 12-month ECL where the credit risk has not increased significantly since initial recognition.</t>
+          <t>Measure the loss allowance at 12-month ECL where the credit risk has not increased significantly since initial recognition.</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
@@ -1396,7 +1400,7 @@
       </c>
       <c r="E8" s="22" t="inlineStr">
         <is>
-          <t>Stage 1 loans take the 12-month PD window in the ECL service; the staging writes the stage every period.</t>
+          <t>Stage 1 loans take the 12-month PD window; the staging writes the stage every period.</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr"/>
@@ -1407,14 +1411,14 @@
       </c>
       <c r="H8" s="22" t="inlineStr">
         <is>
-          <t>Financial Modelling, ECL Calculation: /expected-credit-loss</t>
+          <t>ECL Processing, ECL Calculation: /expected-credit-loss/list</t>
         </is>
       </c>
       <c r="I8" s="22" t="inlineStr"/>
       <c r="J8" s="22" t="inlineStr"/>
       <c r="K8" s="22" t="inlineStr">
         <is>
-          <t>Tests\Feature\Ecl\TimePhasedEclServiceTest</t>
+          <t>Tests\Feature\Ecl\TimePhasedEclServiceTest::test_stage_one_builds_a_twelve_month_marginal_pd_curve_and_discounts_each_shortfall</t>
         </is>
       </c>
     </row>
@@ -1441,33 +1445,33 @@
       </c>
       <c r="E9" s="22" t="inlineStr">
         <is>
-          <t>Stage 2 from 31 days past due in every facility class; days counted from the oldest overdue instalment as the directive counts, with the bucket ageing beside it; a rebuttal of the presumption is a governed setting (staging_rebuttal) whose seeded value cites the directive; the LONG_TERM rule proposing 91 days is seeded future-dated and inactive pending CFO sign-off.</t>
+          <t>Stage 2 from 31 days past due in every facility class, counted from the oldest overdue instalment, with the bucket ageing beside it. The rebuttal is recorded on the threshold rows (staging_thresholds.rebuttal_basis); the LONG_TERM row proposing Stage 2 at 91 days for medium- and long-term facilities only is seeded future-dated (2099) and inactive pending CFO sign-off. The threshold rows are seeded and read-only on screen (a change is a release, not a setting). The staging_rebuttal catalogue setting is shown on Settings but read by no engine.</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
         <is>
-          <t>The O13 rebuttal paper of 8 October.</t>
+          <t>The O13 rebuttal paper of 8 October 2026.</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
         <is>
-          <t>Compliant; the presumption is applied, the rebuttal is governed.</t>
+          <t>Compliant; the presumption is applied and the rebuttal awaits the CFO.</t>
         </is>
       </c>
       <c r="H9" s="22" t="inlineStr">
         <is>
-          <t>Governance Centre, Staging &amp; SICR Rules: /stageing-rules; Data Foundation, Loan Book; Governance Centre: /eir-governance</t>
+          <t>Settings, Staging basis: /setting?tab=staging; IFRS 9 Model Setup, Staging &amp; SICR Rules: /sicr-groups; Governance: Governance Centre /eir-governance</t>
         </is>
       </c>
       <c r="I9" s="22" t="inlineStr"/>
       <c r="J9" s="22" t="inlineStr">
         <is>
-          <t>staging_rebuttal; dpd_basis</t>
+          <t>dpd_basis; staging_rebuttal (shown, not read)</t>
         </is>
       </c>
       <c r="K9" s="22" t="inlineStr">
         <is>
-          <t>Tests\Feature\Eir\StagingThresholdSeederTest; Tests\Feature\Eir\StagingServiceTest</t>
+          <t>Tests\Feature\Eir\StagingThresholdSeederTest::test_the_long_term_stage_2_rebuttal_is_inactive_until_signed; Tests\Feature\Eir\StagingServiceTest</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1488,7 @@
       </c>
       <c r="C10" s="22" t="inlineStr">
         <is>
-          <t>Apply a definition of default consistent with the one used for internal credit risk management; there is a rebuttable presumption that default occurs no later than 90 days past due unless reasonable and supportable information supports a more lagging criterion.</t>
+          <t>Apply a definition of default consistent with internal credit risk management; default occurs no later than 90 days past due unless reasonable and supportable information supports a more lagging criterion.</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -1494,7 +1498,7 @@
       </c>
       <c r="E10" s="22" t="inlineStr">
         <is>
-          <t>Stage 3 from 91 days for a facility of 12 months or less and for the Mega Farm class, and from 181 days for a medium- or long-term facility, as the RBM directive classifies them; the accounting policy's four-consecutive-missed-instalments trigger lifts a loan to Stage 3 beside the day count. The more lagging criterion rests on the directive, cited on each threshold row.</t>
+          <t>Stage 3 from 91 days for a facility of 12 months or less and for the Mega Farm class, and from 181 days for a medium- or long-term facility, as the RBM directive classifies them; the four-consecutive-missed-instalments trigger lifts a loan to Stage 3 beside the day count, reading the chart in force and net cash (216aee2). The more lagging criterion rests on the directive, cited on each threshold row.</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -1509,18 +1513,18 @@
       </c>
       <c r="H10" s="22" t="inlineStr">
         <is>
-          <t>Governance Centre, Staging &amp; SICR Rules: /stageing-rules; Data Foundation, Loan Book</t>
+          <t>Settings, Staging basis: /setting?tab=staging; IFRS 9 Model Setup, Staging &amp; SICR Rules: /sicr-groups</t>
         </is>
       </c>
       <c r="I10" s="22" t="inlineStr"/>
       <c r="J10" s="22" t="inlineStr">
         <is>
-          <t>dpd_basis; stage3_missed_instalments; staging_rebuttal</t>
+          <t>dpd_basis; stage3_missed_instalments</t>
         </is>
       </c>
       <c r="K10" s="22" t="inlineStr">
         <is>
-          <t>Tests\Feature\Eir\StagingServiceTest::test_the_directive_thresholds_by_tenor_class_and_the_bucket_fallback</t>
+          <t>Tests\Feature\Eir\StagingServiceTest::test_the_directive_thresholds_by_tenor_class_and_the_bucket_fallback; Tests\Feature\Eir\StagingThresholdSeederTest::test_medium_and_long_term_facilities_are_stage_3_at_181_days_with_the_rebuttal_cited</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1548,7 @@
       </c>
       <c r="C12" s="22" t="inlineStr">
         <is>
-          <t>ECL is an unbiased, probability-weighted amount determined by evaluating a range of possible outcomes, the time value of money, and reasonable and supportable information about past events, current conditions and forecasts of future economic conditions.</t>
+          <t>ECL is an unbiased, probability-weighted amount determined by evaluating a range of possible outcomes, the time value of money, and reasonable and supportable information about past events, current conditions and forecasts.</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
@@ -1554,22 +1558,22 @@
       </c>
       <c r="E12" s="22" t="inlineStr">
         <is>
-          <t>Probability weighting across scenarios is built as the governed weighting method (the ECL under each scenario, weighted; sensitivity stored with the set); discounting is at the EIR; the forward-looking chain produces fits from the macro series. The PD engine has not run on the clean install and no fit is approved by a MAIIC reviewer, so the weighted ECL is not yet produced for a period.</t>
+          <t>The PD and LGD by segment, the forward-looking route once per scenario and the weighted ECL run for every period; discounting at the EIR is the month-end default since 216aee2. What is missing: no fit is approved by a MAIIC reviewer, so the route holds the PD (overlay at zero); the governed scenario set is approved only under the bootstrap label; the legacy synthetic scenario assumptions are still seeded APPROVED (EclScenarioAssumptionSeeder); and the reports read the undiscounted ecl_value (5.5.17(b) row).</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
         <is>
-          <t>Spec v4 sections 14, 15.</t>
+          <t>Fresh bootstrap maiic_ifrs9_results2 (13 October 2026, before commit 216aee2). Until 14 October 2026 the row said the PD engine had not run on the clean install.</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
         <is>
-          <t>Partially done: the mechanics are in place; the PD run and an approved fit are awaited.</t>
+          <t>Partially done: the mechanics are in place; an approved fit and set, and the discounted figure in the reports, are awaited.</t>
         </is>
       </c>
       <c r="H12" s="22" t="inlineStr">
         <is>
-          <t>Financial Modelling, ECL Calculation: /expected-credit-loss; Governance Centre, Scenario Sets: /scenario-sets</t>
+          <t>ECL Processing, ECL Calculation: /expected-credit-loss/list; Forward-Looking Information, Scenario Sets: /scenario-sets</t>
         </is>
       </c>
       <c r="I12" s="22" t="inlineStr"/>
@@ -1580,7 +1584,7 @@
       </c>
       <c r="K12" s="22" t="inlineStr">
         <is>
-          <t>Tests\Feature\Scenario\ScenarioSetServiceTest; Tests\Feature\Ecl\EclDiscountRateServiceTest</t>
+          <t>Tests\Feature\FLI\FliRouteServiceTest::test_the_ecl_on_the_post_fli_pd_is_the_weighted_ecl_across_scenarios; Tests\Feature\Ecl\TimePhasedEclServiceTest::test_scenario_weights_combine_into_one_allowance</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1611,12 @@
       </c>
       <c r="E13" s="22" t="inlineStr">
         <is>
-          <t>The governed scenario set: three or more scenarios, weights summing to 100, the base at least 40 percent and no single weight above 60, every scenario but the base a shock on the base path; the first set (Base 50, Upside 15, Downside 25, Severe 10) is seeded as a proposal for the CFO, each anchored to a year Malawi has lived through.</t>
+          <t>The governed scenario set: three or more scenarios, weights summing to 100, the base at least 40 percent and no weight above 60, every scenario but the base a shock on the base path; the first set (Base 50, Upside 15, Downside 25, Severe 10) is seeded as a proposal for the CFO. On the fresh bootstrap one set (September 2026) is APPROVED under the bootstrap label.</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
         <is>
-          <t>Spec v4 section 15.</t>
+          <t>Fresh bootstrap maiic_ifrs9_results2 (13 October 2026, before commit 216aee2).</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -1622,7 +1626,7 @@
       </c>
       <c r="H13" s="22" t="inlineStr">
         <is>
-          <t>Governance Centre, Scenario Sets: /scenario-sets</t>
+          <t>Forward-Looking Information, Scenario Sets: /scenario-sets</t>
         </is>
       </c>
       <c r="I13" s="22" t="inlineStr"/>
@@ -1633,7 +1637,7 @@
       </c>
       <c r="K13" s="22" t="inlineStr">
         <is>
-          <t>Tests\Feature\Scenario\ScenarioSetServiceTest</t>
+          <t>Tests\Feature\Scenario\ScenarioSetServiceTest::test_a_set_that_breaks_a_rule_is_refused_with_the_reason</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1654,7 @@
       </c>
       <c r="C14" s="22" t="inlineStr">
         <is>
-          <t>Use information that is reasonably available without undue cost or effort, including forecasts of future economic conditions; where a statistical relationship is used it must be supportable.</t>
+          <t>Use information reasonably available without undue cost or effort, including forecasts of future economic conditions; a statistical relationship used must be supportable.</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
@@ -1660,12 +1664,12 @@
       </c>
       <c r="E14" s="22" t="inlineStr">
         <is>
-          <t>Eleven Malawi macro series from the World Bank with their provenance (source, address, fetched-at, who) and a committed snapshot; the forward-looking chain sweeps every driver against every credit-loss proxy over the lag grid under the guardrail (expected sign, R2 cutoff, p-value, minimum observations) and declines a fit that fails with the reason; the structural-events register (the 2023 devaluation, COVID, the policy-rate cycle, the E-Banker take-on) is read by the diagnostics.</t>
+          <t>Malawi macro series with their provenance (13 variables, 261 data points on the fresh bootstrap; none yet carries a release date, so revisions replace the earlier value); the correlation finder sweeps every driver against every credit-loss proxy over the lag grid under the guardrail (expected sign, R2 cutoff, p-value, minimum observations) and declines a failing fit with the reason. On the fresh bootstrap: 209 fits, 32 applied by the guardrail, 177 declined, none approved.</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
         <is>
-          <t>On the clean install: 209 fits, 39 applied by the guardrail, 170 declined.</t>
+          <t>Fresh bootstrap maiic_ifrs9_results2 (13 October 2026, before commit 216aee2). Until 14 October 2026 the row said 39 applied and 170 declined, from the 8 October install.</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -1675,7 +1679,7 @@
       </c>
       <c r="H14" s="22" t="inlineStr">
         <is>
-          <t>Financial Modelling, Forward-Looking Model: /regression; fli:correlate; fli:method-cards; Data Foundation, Macro Statistics</t>
+          <t>Forward-Looking Information: Overview /fli; Correlation Finder /fli-correlation; Regression /fli-adjustments; transmission methods /fli/transmission-methods; Macro Statistics: /macro-statistics</t>
         </is>
       </c>
       <c r="I14" s="22" t="inlineStr"/>
@@ -1686,7 +1690,7 @@
       </c>
       <c r="K14" s="22" t="inlineStr">
         <is>
-          <t>Tests\Feature\FLI\FliBridgeServiceTest</t>
+          <t>Tests\Feature\FLI\FliBridgeServiceTest; Tests\Feature\Macro\MacroImportPrecedenceTest</t>
         </is>
       </c>
     </row>
@@ -1713,7 +1717,7 @@
       </c>
       <c r="E15" s="22" t="inlineStr">
         <is>
-          <t>Five governed transmission methods, each with a card: what it does, the formula, what it implies, its preconditions checked live against the data with the deciding figure, and a worked example on one loan; a method whose preconditions are not met cannot be selected; the scalar is seeded because the history cannot yet support the richer methods.</t>
+          <t>Governed transmission methods, each with a card (what it does, the formula, its preconditions checked live against the data, a worked example on one loan); a method whose preconditions are not met cannot be selected; the scalar is seeded because the history cannot yet support the richer methods.</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -1728,7 +1732,7 @@
       </c>
       <c r="H15" s="22" t="inlineStr">
         <is>
-          <t>Financial Modelling, Forward-Looking Model: /regression; fli:correlate; fli:method-cards; Governance Centre, the cards inline on the setting: /eir-governance; fli:method-cards</t>
+          <t>Forward-Looking Information: Overview /fli; Correlation Finder /fli-correlation; Regression /fli-adjustments; transmission methods /fli/transmission-methods; Governance: Governance Centre /eir-governance</t>
         </is>
       </c>
       <c r="I15" s="22" t="inlineStr"/>
@@ -1746,7 +1750,7 @@
     <row r="16">
       <c r="A16" s="22" t="inlineStr">
         <is>
-          <t>B5.5.28 to B5.5.30</t>
+          <t>B5.5.1 to B5.5.6, B5.5.28 to B5.5.30</t>
         </is>
       </c>
       <c r="B16" s="22" t="inlineStr">
@@ -1761,41 +1765,45 @@
       </c>
       <c r="D16" s="23" t="inlineStr">
         <is>
-          <t>Partially done</t>
+          <t>Done</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
         <is>
-          <t>Credit-loss proxies are produced for the book and per product group (NPL ratio, Stage 3 share, 12-month default rate), and the segment-specific scalar is a governed method; the PD transition matrices by grade run from their screen and are not yet in the bootstrap chain.</t>
-        </is>
-      </c>
-      <c r="F16" s="22" t="inlineStr"/>
+          <t>PdSegmentationService and LgdSegmentationService measure the PD and LGD per portfolio on the governed basis, a thin segment taking its parent's or the pooled figure under the governed rule, with the lineage on each loan; the Mega Farm programme is its own segment, kept out of MAIIC's PD, LGD and ECL, and a portfolio mixing the two is refused (216aee2). Both run for every period in the bootstrap and the month-end.</t>
+        </is>
+      </c>
+      <c r="F16" s="22" t="inlineStr">
+        <is>
+          <t>Until 14 October 2026 this row was Partially done and said the transition matrices were not in the bootstrap chain.</t>
+        </is>
+      </c>
       <c r="G16" s="22" t="inlineStr">
         <is>
-          <t>Partially done.</t>
+          <t>Compliant.</t>
         </is>
       </c>
       <c r="H16" s="22" t="inlineStr">
         <is>
-          <t>Financial Modelling, Forward-Looking Model: /regression; fli:correlate; fli:method-cards; Financial Modelling, PD Model</t>
+          <t>IFRS 9 Model Setup, PD Model and LGD Model; Reports: PD by portfolio /ifrs9-reports/sector-ecl</t>
         </is>
       </c>
       <c r="I16" s="22" t="inlineStr"/>
       <c r="J16" s="22" t="inlineStr">
         <is>
-          <t>fli_transmission_method</t>
+          <t>pd_segmentation_basis; pd_segment_min_observations; pd_segment_thin_rule; lgd_segment_min_cohort</t>
         </is>
       </c>
       <c r="K16" s="22" t="inlineStr">
         <is>
-          <t>Tests\Feature\FLI\FliBridgeServiceTest</t>
+          <t>Tests\Feature\Pd\PdSegmentationTest::test_each_portfolio_gets_its_own_pd_or_its_parents_with_the_lineage_recorded; Tests\Feature\Ecl\MegaFarmProgrammeSeparationTest::test_the_programme_portfolio_is_kept_out_of_the_maiic_scope_and_a_blended_book_is_refused</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="22" t="inlineStr">
         <is>
-          <t>B5.5.33 to B5.5.35</t>
+          <t>B5.5.55</t>
         </is>
       </c>
       <c r="B17" s="22" t="inlineStr">
@@ -1805,33 +1813,45 @@
       </c>
       <c r="C17" s="22" t="inlineStr">
         <is>
-          <t>The cash shortfalls reflect the cash flows expected from collateral and other credit enhancements that are part of the contractual terms.</t>
+          <t>The cash shortfalls reflect the cash flows expected from collateral and other credit enhancements that are integral to the contractual terms.</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
         <is>
-          <t>Evidence needed from MAIIC</t>
+          <t>Partially done</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
         <is>
-          <t>LGD runs from the LGD screens (monthly and cumulative); the security register (P2_11, 185 rows) is landed and 31 active accounts carry no security on it (the request to Credit of 7 October).</t>
-        </is>
-      </c>
-      <c r="F17" s="22" t="inlineStr"/>
+          <t>The LGD is the Stage 3 cohort workout per portfolio (cure, recovery discounted, write-off as loss; a written-off loan left at nil is no longer a cure since 216aee2). Collateral does not enter it: the engine reads no collateral, and on the fresh bootstrap collateral_registers and collateral_allocations are empty although the E-Banker security register (P2_11, 185 rows) is landed.</t>
+        </is>
+      </c>
+      <c r="F17" s="22" t="inlineStr">
+        <is>
+          <t>Until 14 October 2026 this row was referenced B5.5.33 to B5.5.35 and marked Evidence needed; the collateral link is also Dupleix's to build.</t>
+        </is>
+      </c>
       <c r="G17" s="22" t="inlineStr">
         <is>
-          <t>Evidence needed: the collateral for the 31 accounts; the valuations.</t>
+          <t>Partially done: Credit supplies the collateral and valuations; Dupleix brings collateral into the LGD.</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
         <is>
-          <t>Financial Modelling, LGD Model; Data Foundation, Collateral Register</t>
+          <t>IFRS 9 Model Setup, LGD Model; Collateral Management, Collateral Register: /collateral/register; Reports: LGD and collateral /ifrs9-reports/lgd-collateral</t>
         </is>
       </c>
       <c r="I17" s="22" t="inlineStr"/>
-      <c r="J17" s="22" t="inlineStr"/>
-      <c r="K17" s="22" t="inlineStr"/>
+      <c r="J17" s="22" t="inlineStr">
+        <is>
+          <t>lgd_segment_min_cohort</t>
+        </is>
+      </c>
+      <c r="K17" s="22" t="inlineStr">
+        <is>
+          <t>Tests\Feature\Pd\PdAndLgdEngineTest::test_a_loan_closed_at_nil_is_not_a_cure_and_a_nil_start_balance_is_no_member</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="22" t="inlineStr">
@@ -1846,35 +1866,39 @@
       </c>
       <c r="C18" s="22" t="inlineStr">
         <is>
-          <t>Discount the expected credit losses at the EIR determined at initial recognition.</t>
+          <t>Discount the expected credit losses at the EIR determined at initial recognition (or an approximation).</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
         <is>
-          <t>Done</t>
+          <t>Partially done</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
         <is>
-          <t>EclDiscountRateService takes the locked EIR of the loan (the contractual rate where none is locked, and says so on the row); the bootstrap solves and locks the EIR before the ECL for this reason.</t>
-        </is>
-      </c>
-      <c r="F18" s="22" t="inlineStr"/>
+          <t>EclDiscountRateService takes the loan's locked EIR; an unlocked or missing EIR is unresolved, never defaulted, and a floating loan's rate is labelled a proxy; a Stage 3 loss at the reporting date needs no rate. Since 216aee2 the month-end and the bootstrap run discounted by default: ecl_value keeps the engine's measure and ecl_value_discounted holds the discounted allowance, shown on the ECL screen. But the IFRS 9 note, the ECL reconciliation, the RBM Return and the other reports still read ecl_value, so the figure they carry is undiscounted. On the fresh bootstrap at September 2026, 62 main-book loans are discounted (7.12bn) and 72 are unresolved.</t>
+        </is>
+      </c>
+      <c r="F18" s="22" t="inlineStr">
+        <is>
+          <t>Fresh bootstrap maiic_ifrs9_results2 (13 October 2026, before commit 216aee2). Until 14 October 2026 the row said 'the contractual rate where none is locked', which the code never did.</t>
+        </is>
+      </c>
       <c r="G18" s="22" t="inlineStr">
         <is>
-          <t>Compliant.</t>
+          <t>Partially done: the discounted allowance is computed; the reports must carry it.</t>
         </is>
       </c>
       <c r="H18" s="22" t="inlineStr">
         <is>
-          <t>Financial Modelling, ECL Calculation: /expected-credit-loss</t>
+          <t>ECL Processing, ECL Calculation: /expected-credit-loss/list</t>
         </is>
       </c>
       <c r="I18" s="22" t="inlineStr"/>
       <c r="J18" s="22" t="inlineStr"/>
       <c r="K18" s="22" t="inlineStr">
         <is>
-          <t>Tests\Feature\Ecl\EclDiscountRateServiceTest</t>
+          <t>Tests\Feature\Ecl\EclDiscountRateServiceTest::test_an_unlocked_or_missing_eir_is_unresolved_never_defaulted; Tests\Feature\Ecl\EclGoldenNumberTest::discounted_mode_keeps_undiscounted_ecl_and_names_unresolved_contracts</t>
         </is>
       </c>
     </row>
@@ -1908,23 +1932,31 @@
       </c>
       <c r="E20" s="22" t="inlineStr">
         <is>
-          <t>No write-off has been posted in E-Banker since the take-on (DD_16i returned no rows); the policy is MAIIC's to state.</t>
-        </is>
-      </c>
-      <c r="F20" s="22" t="inlineStr"/>
+          <t>WriteOffClassifier (220a5a6) identifies ledger write-offs (type 300; a batch debiting GL 1064; ACCOUNT CLOSURE on a status-H account) for the loan-book build, the contract inputs and the EIR cash; the PD cohort counts a write-off as a default (216aee2); the register records a write-off not on the loan account under two-person approval. On the fresh bootstrap: 22 ledger write-offs of 60,778,466.86; the register is empty.</t>
+        </is>
+      </c>
+      <c r="F20" s="22" t="inlineStr">
+        <is>
+          <t>Fresh bootstrap maiic_ifrs9_results2 (13 October 2026, before commit 216aee2). Until 14 October 2026 the row said no write-off had been posted since the take-on.</t>
+        </is>
+      </c>
       <c r="G20" s="22" t="inlineStr">
         <is>
-          <t>Evidence needed: the write-off policy.</t>
+          <t>Evidence needed: MAIIC's write-off policy and Finance's confirmation of status H.</t>
         </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
         <is>
-          <t>Financial Modelling, ECL Calculation: /expected-credit-loss</t>
+          <t>EIR Data, Write-offs: /eir-write-offs</t>
         </is>
       </c>
       <c r="I20" s="22" t="inlineStr"/>
       <c r="J20" s="22" t="inlineStr"/>
-      <c r="K20" s="22" t="inlineStr"/>
+      <c r="K20" s="22" t="inlineStr">
+        <is>
+          <t>Tests\Feature\Eir\WriteOffTest::test_a_closure_credit_in_a_batch_that_debits_the_write_off_gl_is_a_write_off; Tests\Feature\Pd\PdSegmentationTest::test_a_nil_start_balance_is_no_observation_and_a_write_off_in_the_window_is_a_default</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
@@ -1956,22 +1988,22 @@
       </c>
       <c r="E22" s="22" t="inlineStr">
         <is>
-          <t>The system holds a November 2025 Mega Farm loan book of 3,490 loans across six GLs (K54.85 bn), found by the build, staged under the MEGA_FARM class (91 days); the programme's treatment (decision D30: out of the EIR engine, in the ECL module, 5 percent share on net) and the PD method (seeded: the agricultural-sector PD scaled to the programme) are governed settings awaiting the CFO's confirmation.</t>
+          <t>The programme's monthly books (MF_01 and MF_03) are landed: on the fresh bootstrap 3,692 loans on six of the programme's seven GLs (1050301 to 1050305 and 1050307) with 56.18bn gross at September 2026, 3,559 of them over 90 days past due. Since 216aee2 the programme is segmented as its own portfolio, kept out of MAIIC's PD, LGD and ECL, and provided by megafarm:ecl from its own LGD cohort under the governed PD method; MAIIC's share is read from the mega_farms_scope text (it falls back to 1.0 when the text names no share). Not built: the interest split, the maize receivable and the fund liability of spec 16.4 and 16.5 (they wait on D30).</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
         <is>
-          <t>Spec v4 section 16; the O22 paper of 8 October.</t>
+          <t>Fresh bootstrap maiic_ifrs9_results2 (13 October 2026, before commit 216aee2). Until 14 October 2026 the row said 3,490 loans (K54.85bn) from a November 2025 book.</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
         <is>
-          <t>Evidence needed: the CFO's confirmation of D30; how the K39.76 bn provision of 2025 was arrived at; the monthly Mega Farm books.</t>
+          <t>Evidence needed: the CFO's confirmation of D30; how the K39.76bn provision of 2025 was arrived at.</t>
         </is>
       </c>
       <c r="H22" s="22" t="inlineStr">
         <is>
-          <t>Financial Modelling, Mega Farm Programme: /megafarm; Governance Centre: /eir-governance</t>
+          <t>ECL Processing, Mega Farm Programme: /megafarm; Governance: Governance Centre /eir-governance</t>
         </is>
       </c>
       <c r="I22" s="22" t="inlineStr"/>
@@ -1980,7 +2012,11 @@
           <t>mega_farms_scope; megafarm_pd_method; megafarm_scalar_ceiling</t>
         </is>
       </c>
-      <c r="K22" s="22" t="inlineStr"/>
+      <c r="K22" s="22" t="inlineStr">
+        <is>
+          <t>Tests\Feature\Ecl\MegaFarmProgrammeSeparationTest::test_the_programme_lgd_is_its_own_cohort_and_a_missing_cohort_declines</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:K22"/>
@@ -2033,7 +2069,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2110,27 +2146,27 @@
       </c>
       <c r="B5" s="24" t="inlineStr">
         <is>
-          <t>5.5.17</t>
+          <t>5.5.1, 5.5.17</t>
         </is>
       </c>
       <c r="C5" s="22" t="inlineStr">
         <is>
-          <t>The PD and LGD of the clean install are the bootstrap's, not MAIIC's</t>
+          <t>The PD, LGD and ECL are the bootstrap's, not MAIIC's</t>
         </is>
       </c>
       <c r="D5" s="22" t="inlineStr">
         <is>
-          <t>PdEngineService and LgdEngineService run the transition matrix and the cohort workout under the bootstrap label; no MAIIC reviewer has key-locked a matrix or an LGD calculation in the system.</t>
+          <t>The PD and LGD engines run under the bootstrap label; no MAIIC reviewer has approved a segment run, a fit or the scenario set. On the fresh bootstrap the main-book ECL at September 2026 is 11.57bn undiscounted (7.12bn discounted on 62 loans, 72 unresolved). (Until 14 October 2026 this finding quoted 8.33bn, which the Contract Schedule 1 workbook gave as 8.94bn; neither is current.)</t>
         </is>
       </c>
       <c r="E5" s="22" t="inlineStr">
         <is>
-          <t>The ECL of 8.33bn at August 2026 is a system figure awaiting review.</t>
+          <t>The ECL is a system figure awaiting review.</t>
         </is>
       </c>
       <c r="F5" s="22" t="inlineStr">
         <is>
-          <t>A reviewer key-locks the matrix and the LGD on their screens; the ECL is then re-run under the approved scenario set.</t>
+          <t>A reviewer approves the segment runs, a fit and the set; the month is re-run discounted and signed.</t>
         </is>
       </c>
       <c r="G5" s="22" t="inlineStr">
@@ -2162,17 +2198,17 @@
       </c>
       <c r="D6" s="22" t="inlineStr">
         <is>
-          <t>The chain applied 39 fits by the guardrail; approval of a fit for use in the FLI route is a maker-checker decision not yet taken.</t>
+          <t>On the fresh bootstrap the guardrail applied 32 of 209 fits and declined 177; none is approved for the route.</t>
         </is>
       </c>
       <c r="E6" s="22" t="inlineStr">
         <is>
-          <t>The forward-looking adjustment is the manual overlay at zero until then.</t>
+          <t>The forward-looking adjustment is the overlay at zero until then.</t>
         </is>
       </c>
       <c r="F6" s="22" t="inlineStr">
         <is>
-          <t>A reviewer approves a fit on the FLI Adjustments screen; a second person reviews.</t>
+          <t>A reviewer approves a fit on the Regression (FLI adjustments) screen; a second person reviews.</t>
         </is>
       </c>
       <c r="G6" s="22" t="inlineStr">
@@ -2199,12 +2235,12 @@
       </c>
       <c r="C7" s="22" t="inlineStr">
         <is>
-          <t>The Mega Farm provision basis is undocumented in the system</t>
+          <t>The Mega Farm provision basis is undocumented</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
         <is>
-          <t>The 2025 statements carry K39.76 bn against K48.7 bn Stage 3; the November 2025 book in the system is mostly Stage 1 by days past due.</t>
+          <t>The 2025 statements carry K39.76bn against K48.7bn Stage 3. On the fresh bootstrap (staging before 216aee2) the December 2025 programme book of 3,692 loans (54.50bn) is 3,219 loans Stage 1 (47.25bn) and 471 Stage 3 (7.25bn).</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -2214,15 +2250,99 @@
       </c>
       <c r="F7" s="22" t="inlineStr">
         <is>
-          <t>The CFO confirms D30 and the provisioning method; the monthly Mega Farm books are loaded by the feed (MF_01 to MF_08).</t>
+          <t>The CFO confirms D30 and the provisioning method; the next bootstrap on 216aee2 restages the programme on the chart in force.</t>
         </is>
       </c>
       <c r="G7" s="22" t="inlineStr">
         <is>
-          <t>Dr Thom / Barry</t>
+          <t>Dr Thom / Dupleix</t>
         </is>
       </c>
       <c r="H7" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="22" t="inlineStr">
+        <is>
+          <t>F4</t>
+        </is>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>5.5.17(b)</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>The reports carry the undiscounted allowance</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>The discounted allowance is held in ecl_value_discounted; the IFRS 9 note, ECL reconciliation, RBM Return and other reports read ecl_value.</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>The disclosed allowance is undiscounted.</t>
+        </is>
+      </c>
+      <c r="F8" s="22" t="inlineStr">
+        <is>
+          <t>Point the note and the reports at the booked (discounted) allowance, with the undiscounted measure as a reconciling line.</t>
+        </is>
+      </c>
+      <c r="G8" s="22" t="inlineStr">
+        <is>
+          <t>Dupleix</t>
+        </is>
+      </c>
+      <c r="H8" s="22" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>B5.5.55</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>Collateral is not in the LGD</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>The LGD engine reads no collateral; the collateral register is empty on the fresh bootstrap.</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="inlineStr">
+        <is>
+          <t>The cash flows from collateral are not reflected in the shortfall.</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>Credit supplies the collateral and valuations; Dupleix adds the collateral recovery to the LGD.</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t>Credit / Dupleix</t>
+        </is>
+      </c>
+      <c r="H9" s="22" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
@@ -2230,14 +2350,16 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="H5:H7" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H5:H9" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Open,In progress,Closed,Deferred"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="A2" location="'Contents'!A1" display="Back to Contents"/>
-    <hyperlink ref="B5" location="'Audit'!A12" display="5.5.17"/>
+    <hyperlink ref="B5" location="'Audit'!A6" display="5.5.1, 5.5.17"/>
     <hyperlink ref="B7" location="'Audit'!A22" display="16"/>
+    <hyperlink ref="B8" location="'Audit'!A12" display="5.5.17(b)"/>
+    <hyperlink ref="B9" location="'Audit'!A17" display="B5.5.55"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -2251,7 +2373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="64" customWidth="1" min="1" max="1"/>
@@ -2279,7 +2401,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-09 00:03:13 from maiic_ifrs9_bootstrap. The PASS/FAIL in column E is a formula on columns B and C, so it recomputes if a figure is typed over.</t>
+          <t>Generated 2026-10-14 08:30:38 from maiic_ifrs9_results2. The PASS/FAIL in column E is a formula on columns B and C, so it recomputes if a figure is typed over.</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2461,7 @@
     <row r="6">
       <c r="A6" s="22" t="inlineStr">
         <is>
-          <t>Derived carrying amount against the stored report (over 2 cents)</t>
+          <t>Derived carrying amount against the stored report, in-scope loan GLs (over 2 cents)</t>
         </is>
       </c>
       <c r="B6" s="22" t="inlineStr">
@@ -2349,7 +2471,7 @@
       </c>
       <c r="C6" s="22" t="inlineStr">
         <is>
-          <t>0 of 2361 account-months</t>
+          <t>0 of 2495 account-months</t>
         </is>
       </c>
       <c r="D6" s="22" t="n">
@@ -2364,20 +2486,24 @@
     <row r="7">
       <c r="A7" s="22" t="inlineStr">
         <is>
-          <t>Year-end interest batch contra on 4215</t>
-        </is>
-      </c>
-      <c r="B7" s="25" t="n">
-        <v>32956675.55</v>
-      </c>
-      <c r="C7" s="25" t="n">
-        <v>32956675.55</v>
+          <t>Mega Farm: account-months whose MF_03 ledger differs from the Loan Book Report (reported, not a test)</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>77540 account-months</t>
+        </is>
       </c>
       <c r="D7" s="22" t="n">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="E7" s="26">
-        <f>IF(ABS(B7-C7)&lt;=D7,"PASS","FAIL")</f>
+        <f>IF(B7=C7,"PASS","FAIL")</f>
         <v/>
       </c>
       <c r="F7" s="22" t="inlineStr"/>
@@ -2385,17 +2511,17 @@
     <row r="8">
       <c r="A8" s="22" t="inlineStr">
         <is>
-          <t>Year-end interest batch contra on 4216</t>
+          <t>Year-end interest batch contra on 4215</t>
         </is>
       </c>
       <c r="B8" s="25" t="n">
-        <v>-21733262.7</v>
+        <v>32956675.55</v>
       </c>
       <c r="C8" s="25" t="n">
-        <v>-21733262.7</v>
+        <v>32956675.55</v>
       </c>
       <c r="D8" s="22" t="n">
-        <v>0.01</v>
+        <v>1</v>
       </c>
       <c r="E8" s="26">
         <f>IF(ABS(B8-C8)&lt;=D8,"PASS","FAIL")</f>
@@ -2406,17 +2532,17 @@
     <row r="9">
       <c r="A9" s="22" t="inlineStr">
         <is>
-          <t>Loan book 1050101 at 31 Dec 2025 against the trial balance</t>
+          <t>Year-end interest batch contra on 4216</t>
         </is>
       </c>
       <c r="B9" s="25" t="n">
-        <v>1368737810.68</v>
+        <v>-21733262.7</v>
       </c>
       <c r="C9" s="25" t="n">
-        <v>1368737810.68</v>
+        <v>-21733262.7</v>
       </c>
       <c r="D9" s="22" t="n">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="E9" s="26">
         <f>IF(ABS(B9-C9)&lt;=D9,"PASS","FAIL")</f>
@@ -2427,14 +2553,14 @@
     <row r="10">
       <c r="A10" s="22" t="inlineStr">
         <is>
-          <t>Loan book 1050102 at 31 Dec 2025 against the trial balance</t>
+          <t>Loan book 1050101 at 31 Dec 2025 against the trial balance</t>
         </is>
       </c>
       <c r="B10" s="25" t="n">
-        <v>6434045052.56</v>
+        <v>1368737810.68</v>
       </c>
       <c r="C10" s="25" t="n">
-        <v>6434045052.56</v>
+        <v>1368737810.68</v>
       </c>
       <c r="D10" s="22" t="n">
         <v>1</v>
@@ -2448,14 +2574,14 @@
     <row r="11">
       <c r="A11" s="22" t="inlineStr">
         <is>
-          <t>Loan book 1050201 at 31 Dec 2025 against the trial balance (accepted exception, spec 3.5: -400,000.00)</t>
+          <t>Loan book 1050102 at 31 Dec 2025 against the trial balance</t>
         </is>
       </c>
       <c r="B11" s="25" t="n">
-        <v>1402393139.46</v>
+        <v>6434045052.56</v>
       </c>
       <c r="C11" s="25" t="n">
-        <v>1401993139.46</v>
+        <v>6434045052.56</v>
       </c>
       <c r="D11" s="22" t="n">
         <v>1</v>
@@ -2469,14 +2595,14 @@
     <row r="12">
       <c r="A12" s="22" t="inlineStr">
         <is>
-          <t>Loan book 1050202 at 31 Dec 2025 against the trial balance (accepted exception, spec 3.5: 1,000,000.00)</t>
+          <t>Loan book 1050201 at 31 Dec 2025 against the trial balance (accepted exception, spec 3.5: -400,000.00)</t>
         </is>
       </c>
       <c r="B12" s="25" t="n">
-        <v>3808288656.15</v>
+        <v>1402393139.46</v>
       </c>
       <c r="C12" s="25" t="n">
-        <v>3809288656.15</v>
+        <v>1401993139.46</v>
       </c>
       <c r="D12" s="22" t="n">
         <v>1</v>
@@ -2490,14 +2616,14 @@
     <row r="13">
       <c r="A13" s="22" t="inlineStr">
         <is>
-          <t>Loan book 1050401 at 31 Dec 2025 against the trial balance</t>
+          <t>Loan book 1050202 at 31 Dec 2025 against the trial balance (accepted exception, spec 3.5: 1,000,000.00)</t>
         </is>
       </c>
       <c r="B13" s="25" t="n">
-        <v>1827148120.69</v>
+        <v>3808288656.15</v>
       </c>
       <c r="C13" s="25" t="n">
-        <v>1827148120.69</v>
+        <v>3809288656.15</v>
       </c>
       <c r="D13" s="22" t="n">
         <v>1</v>
@@ -2508,8 +2634,29 @@
       </c>
       <c r="F13" s="22" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" s="22" t="inlineStr">
+        <is>
+          <t>Loan book 1050401 at 31 Dec 2025 against the trial balance</t>
+        </is>
+      </c>
+      <c r="B14" s="25" t="n">
+        <v>1827148120.69</v>
+      </c>
+      <c r="C14" s="25" t="n">
+        <v>1827148120.69</v>
+      </c>
+      <c r="D14" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="26">
+        <f>IF(ABS(B14-C14)&lt;=D14,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F14" s="22" t="inlineStr"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="E5:E13">
+  <conditionalFormatting sqref="E5:E14">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$E5="PASS"</formula>
     </cfRule>

--- a/docs/compliance/IFRS9_Impairment_Compliance_Audit.xlsx
+++ b/docs/compliance/IFRS9_Impairment_Compliance_Audit.xlsx
@@ -1445,12 +1445,12 @@
       </c>
       <c r="E9" s="22" t="inlineStr">
         <is>
-          <t>Stage 2 from 31 days past due in every facility class, counted from the oldest overdue instalment, with the bucket ageing beside it. The rebuttal is recorded on the threshold rows (staging_thresholds.rebuttal_basis); the LONG_TERM row proposing Stage 2 at 91 days for medium- and long-term facilities only is seeded future-dated (2099) and inactive pending CFO sign-off. The threshold rows are seeded and read-only on screen (a change is a release, not a setting). The staging_rebuttal catalogue setting is shown on Settings but read by no engine.</t>
+          <t>Stage 2 from 31 days past due in every facility class, counted from the oldest overdue instalment, with the bucket ageing beside it. The rebuttal is recorded on the threshold rows (staging_thresholds.rebuttal_basis); the LONG_TERM row proposing Stage 2 at 91 days for medium- and long-term facilities only is seeded future-dated (2099) and inactive pending CFO sign-off. Since 14 October 2026 a threshold row is proposed by one person and approved by another on Settings, Staging basis, forward only and never into a locked month, and staging reads only approved rows, at the period end, with no 31/181 fallback in the legacy importer (audit H11). The staging_rebuttal catalogue setting is marked recorded, not yet applied: the rebuttal is the threshold row with its evidence.</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
         <is>
-          <t>The O13 rebuttal paper of 8 October 2026.</t>
+          <t>The O13 rebuttal paper of 8 October 2026. Until 14 October 2026 the threshold rows were seeded and read-only on screen.</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
@@ -1466,12 +1466,12 @@
       <c r="I9" s="22" t="inlineStr"/>
       <c r="J9" s="22" t="inlineStr">
         <is>
-          <t>dpd_basis; staging_rebuttal (shown, not read)</t>
+          <t>dpd_basis; staging_rebuttal (recorded, not yet applied)</t>
         </is>
       </c>
       <c r="K9" s="22" t="inlineStr">
         <is>
-          <t>Tests\Feature\Eir\StagingThresholdSeederTest::test_the_long_term_stage_2_rebuttal_is_inactive_until_signed; Tests\Feature\Eir\StagingServiceTest</t>
+          <t>Tests\Feature\Eir\StagingThresholdSeederTest::test_the_long_term_stage_2_rebuttal_is_inactive_until_signed; Tests\Feature\Eir\GoLiveControlsTest::test_a_threshold_is_proposed_by_one_person_and_approved_by_another_before_staging_reads_it; Tests\Feature\Eir\StagingClassifierTest::test_with_no_rule_in_force_the_classifier_stops_and_names_it; Tests\Feature\Eir\StagingServiceTest</t>
         </is>
       </c>
     </row>
@@ -1876,17 +1876,17 @@
       </c>
       <c r="E18" s="22" t="inlineStr">
         <is>
-          <t>EclDiscountRateService takes the loan's locked EIR; an unlocked or missing EIR is unresolved, never defaulted, and a floating loan's rate is labelled a proxy; a Stage 3 loss at the reporting date needs no rate. Since 216aee2 the month-end and the bootstrap run discounted by default: ecl_value keeps the engine's measure and ecl_value_discounted holds the discounted allowance, shown on the ECL screen. But the IFRS 9 note, the ECL reconciliation, the RBM Return and the other reports still read ecl_value, so the figure they carry is undiscounted. On the fresh bootstrap at September 2026, 62 main-book loans are discounted (7.12bn) and 72 are unresolved.</t>
+          <t>TimePhasedEclService discounts each loan's expected shortfalls at its locked original EIR and a floating-rate loan's at its current EIR for the month (EIR_CURRENT_FLOATING: the rate the revenue run accrued at, or the same D38 re-estimation from the rate charged; B5.5.44); an unlocked or missing EIR, or a floating loan with no current EIR, is unresolved with the reason, never defaulted or given the original rate; a Stage 3 loss at the reporting date needs no rate. Since 14 October 2026 EclDiscountRateService (the LGD recovery discounting) applies the same rule, so no basis is labelled EIR_ORIGINAL_FLOATING_PROXY any more. Since 216aee2 the month-end and the bootstrap run discounted by default: ecl_value keeps the engine's measure and ecl_value_discounted holds the discounted allowance, shown on the ECL screen. Since 14 October 2026 every report carries the booked allowance (BookedEcl: discounted at the original EIR; the Mega Farm programme measure; a loan with no discounted figure at its undiscounted ECL, counted and named), with the reconciliation from the reporting-date measure (the lifetime projection and the effect of discounting); the IFRS 9 note fails closed while any loan lacks its discounted allowance. On the fresh bootstrap at September 2026, 62 main-book loans are discounted (7,118,643,553.12) and 38 with an ECL have no discounted figure (4,460,558,036.40 undiscounted; most without a locked EIR).</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
         <is>
-          <t>Fresh bootstrap maiic_ifrs9_results2 (13 October 2026, before commit 216aee2). Until 14 October 2026 the row said 'the contractual rate where none is locked', which the code never did.</t>
+          <t>Fresh bootstrap maiic_ifrs9_results2 (13 October 2026, before commit 216aee2). Until 14 October 2026 the row said 'the contractual rate where none is locked', which the code never did; and the reports read the undiscounted ecl_value.</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
         <is>
-          <t>Partially done: the discounted allowance is computed; the reports must carry it.</t>
+          <t>Partially done: the reports carry the discounted allowance; 38 loans still need a locked EIR before the allowance is wholly discounted.</t>
         </is>
       </c>
       <c r="H18" s="22" t="inlineStr">
@@ -1898,7 +1898,7 @@
       <c r="J18" s="22" t="inlineStr"/>
       <c r="K18" s="22" t="inlineStr">
         <is>
-          <t>Tests\Feature\Ecl\EclDiscountRateServiceTest::test_an_unlocked_or_missing_eir_is_unresolved_never_defaulted; Tests\Feature\Ecl\EclGoldenNumberTest::discounted_mode_keeps_undiscounted_ecl_and_names_unresolved_contracts</t>
+          <t>Tests\Feature\Ecl\EclDiscountRateServiceTest::test_an_unlocked_or_missing_eir_is_unresolved_never_defaulted; Tests\Feature\Ecl\EclDiscountRateServiceTest::test_a_floating_facility_is_discounted_at_its_current_eir_not_the_original; Tests\Feature\Ecl\TimePhasedEclFloatingRateTest::test_a_floating_loan_with_no_rate_charged_for_the_month_is_unresolved_never_discounted_at_the_original_eir; Tests\Feature\Ecl\EclGoldenNumberTest::discounted_mode_without_the_time_phased_engine_is_refused_never_proxied; Tests\Feature\Reports\BookedAllowanceAndWriteOffsTest::test_the_basis_of_the_allowance_names_the_loans_without_a_discounted_figure</t>
         </is>
       </c>
     </row>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="E20" s="22" t="inlineStr">
         <is>
-          <t>WriteOffClassifier (220a5a6) identifies ledger write-offs (type 300; a batch debiting GL 1064; ACCOUNT CLOSURE on a status-H account) for the loan-book build, the contract inputs and the EIR cash; the PD cohort counts a write-off as a default (216aee2); the register records a write-off not on the loan account under two-person approval. On the fresh bootstrap: 22 ledger write-offs of 60,778,466.86; the register is empty.</t>
+          <t>WriteOffClassifier (220a5a6) identifies ledger write-offs (type 300; a batch debiting GL 1064; ACCOUNT CLOSURE on a status-H account) for the loan-book build, the contract inputs and the EIR cash; the PD cohort counts a write-off as a default (216aee2); the register records a write-off not on the loan account under two-person approval; since 14 October 2026 the same source (WriteOffSource) feeds the IFRS 9 note, the reconciliations and the RBM Return, and the monthly feed M09_01 is read for write-off batch legs. On the fresh bootstrap: 22 ledger write-offs of 60,778,466.86 (20 of them, 38,492,032.54, between December 2025 and September 2026); the register is empty.</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -1954,7 +1954,7 @@
       <c r="J20" s="22" t="inlineStr"/>
       <c r="K20" s="22" t="inlineStr">
         <is>
-          <t>Tests\Feature\Eir\WriteOffTest::test_a_closure_credit_in_a_batch_that_debits_the_write_off_gl_is_a_write_off; Tests\Feature\Pd\PdSegmentationTest::test_a_nil_start_balance_is_no_observation_and_a_write_off_in_the_window_is_a_default</t>
+          <t>Tests\Feature\Eir\WriteOffTest::test_a_closure_credit_in_a_batch_that_debits_the_write_off_gl_is_a_write_off; Tests\Feature\Eir\WriteOffTest::test_a_write_off_batch_in_the_monthly_ledger_feed_is_read; Tests\Feature\Pd\PdSegmentationTest::test_a_nil_start_balance_is_no_observation_and_a_write_off_in_the_window_is_a_default</t>
         </is>
       </c>
     </row>
@@ -2282,27 +2282,27 @@
       </c>
       <c r="D8" s="22" t="inlineStr">
         <is>
-          <t>The discounted allowance is held in ecl_value_discounted; the IFRS 9 note, ECL reconciliation, RBM Return and other reports read ecl_value.</t>
+          <t>The discounted allowance is held in ecl_value_discounted; the IFRS 9 note, ECL reconciliation, RBM Return and other reports read ecl_value. Status 14 October 2026: the reports carry the booked allowance with the undiscounted measure as a reconciling line, and name the loans with no discounted figure (38 at September 2026); the note fails closed until there are none.</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
         <is>
-          <t>The disclosed allowance is undiscounted.</t>
+          <t>The disclosed allowance is not wholly discounted until those loans carry a locked EIR.</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
         <is>
-          <t>Point the note and the reports at the booked (discounted) allowance, with the undiscounted measure as a reconciling line.</t>
+          <t>Lock the EIRs of the named loans (fee reviews), then run the month-end ECL again.</t>
         </is>
       </c>
       <c r="G8" s="22" t="inlineStr">
         <is>
-          <t>Dupleix</t>
+          <t>Dupleix / MAIIC reviewers</t>
         </is>
       </c>
       <c r="H8" s="22" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>In progress</t>
         </is>
       </c>
     </row>
@@ -2373,7 +2373,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="64" customWidth="1" min="1" max="1"/>
@@ -2401,7 +2401,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-14 08:30:38 from maiic_ifrs9_results2. The PASS/FAIL in column E is a formula on columns B and C, so it recomputes if a figure is typed over.</t>
+          <t>Generated 2026-10-14 10:44:30 from maiic_ifrs9_wire. The PASS/FAIL in column E is a formula on columns B and C, so it recomputes if a figure is typed over.</t>
         </is>
       </c>
     </row>
@@ -2655,8 +2655,1424 @@
       </c>
       <c r="F14" s="22" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" s="22" t="inlineStr">
+        <is>
+          <t>Pack inventory: ebanker-pack-2026-10-09: every file as committed and landed with its manifest rows and SHA-256; 13 received files not landed, each with its reason in the manifest</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>12 extracts, 111,513 rows</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>12 extracts, 111,513 rows</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E15" s="26">
+        <f>IF(B15=C15,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F15" s="22" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="22" t="inlineStr">
+        <is>
+          <t>Pack inventory: ebanker-pack-2026-10-12: every file as committed and landed with its manifest rows and SHA-256; 2 received files not landed, each with its reason in the manifest</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>39 extracts, 511,785 rows</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>39 extracts, 511,785 rows</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E16" s="26">
+        <f>IF(B16=C16,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F16" s="22" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="22" t="inlineStr">
+        <is>
+          <t>Pack inventory: ebanker-pack-2026-10-12-p5: every file as committed and landed with its manifest rows and SHA-256; 1 received files not landed, each with its reason in the manifest</t>
+        </is>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>8 extracts, 470 rows</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>8 extracts, 470 rows</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E17" s="26">
+        <f>IF(B17=C17,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F17" s="22" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="22" t="inlineStr">
+        <is>
+          <t>Pack inventory: ebanker-pack-2026-10-12-p6: every file as committed and landed with its manifest rows and SHA-256; 0 received files not landed, each with its reason in the manifest</t>
+        </is>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>3 extracts, 236 rows</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>3 extracts, 236 rows</t>
+        </is>
+      </c>
+      <c r="D18" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E18" s="26">
+        <f>IF(B18=C18,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F18" s="22" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="inlineStr">
+        <is>
+          <t>Pack inventory: ebanker-pack-2026-10-13-p7: every file as committed and landed with its manifest rows and SHA-256; 0 received files not landed, each with its reason in the manifest</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>6 extracts, 32,244 rows</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>6 extracts, 32,244 rows</t>
+        </is>
+      </c>
+      <c r="D19" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E19" s="26">
+        <f>IF(B19=C19,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F19" s="22" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="22" t="inlineStr">
+        <is>
+          <t>Pack inventory: ebanker-pack-2026-10-13-p8: every file as committed and landed with its manifest rows and SHA-256; 6 received files not landed, each with its reason in the manifest</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>4 extracts, 103 rows</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>4 extracts, 103 rows</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E20" s="26">
+        <f>IF(B20=C20,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F20" s="22" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="22" t="inlineStr">
+        <is>
+          <t>Pack inventory: ebanker-pack-2026-10-14: every file as committed and landed with its manifest rows and SHA-256; 13 received files not landed, each with its reason in the manifest</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>2 extracts, 426 rows</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>2 extracts, 426 rows</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E21" s="26">
+        <f>IF(B21=C21,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F21" s="22" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="22" t="inlineStr">
+        <is>
+          <t>Pack inventory: manifest.json (packs 1 and 2, data dictionary, trial balances, take-on): every file as committed and landed with its manifest rows and SHA-256; 3 received files not landed, each with its reason in the manifest; 30 workbooks and scripts, 23 landed by the bootstrap</t>
+        </is>
+      </c>
+      <c r="B22" s="22" t="inlineStr">
+        <is>
+          <t>54 extracts, 85,174 rows, 23 workbooks</t>
+        </is>
+      </c>
+      <c r="C22" s="22" t="inlineStr">
+        <is>
+          <t>54 extracts, 85,174 rows, 23 workbooks</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E22" s="26">
+        <f>IF(B22=C22,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F22" s="22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="inlineStr">
+        <is>
+          <t>Take-on worksheet (CV_10) against the take-on postings of 31 Jul 2024: term loans on the worksheet with take-on postings</t>
+        </is>
+      </c>
+      <c r="B23" s="25" t="n">
+        <v>77</v>
+      </c>
+      <c r="C23" s="25" t="n">
+        <v>77</v>
+      </c>
+      <c r="D23" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E23" s="26">
+        <f>IF(ABS(B23-C23)&lt;=D23,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F23" s="22" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="22" t="inlineStr">
+        <is>
+          <t>Take-on worksheet (CV_10) against the take-on postings of 31 Jul 2024: loans whose principal taken on (301) = NEWDISBURS_AMT, to the cent</t>
+        </is>
+      </c>
+      <c r="B24" s="25" t="n">
+        <v>76</v>
+      </c>
+      <c r="C24" s="25" t="n">
+        <v>76</v>
+      </c>
+      <c r="D24" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E24" s="26">
+        <f>IF(ABS(B24-C24)&lt;=D24,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F24" s="22" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="22" t="inlineStr">
+        <is>
+          <t>Take-on worksheet (CV_10) against the take-on postings of 31 Jul 2024: loans whose opening interest (303) = TOTAL_INT_CHARG, to the cent</t>
+        </is>
+      </c>
+      <c r="B25" s="25" t="n">
+        <v>76</v>
+      </c>
+      <c r="C25" s="25" t="n">
+        <v>76</v>
+      </c>
+      <c r="D25" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E25" s="26">
+        <f>IF(ABS(B25-C25)&lt;=D25,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F25" s="22" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="22" t="inlineStr">
+        <is>
+          <t>Take-on worksheet (CV_10) against the take-on postings of 31 Jul 2024: loans whose opening recoveries (305) = TOTA_REPAY_UPTO, to the cent</t>
+        </is>
+      </c>
+      <c r="B26" s="25" t="n">
+        <v>72</v>
+      </c>
+      <c r="C26" s="25" t="n">
+        <v>72</v>
+      </c>
+      <c r="D26" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E26" s="26">
+        <f>IF(ABS(B26-C26)&lt;=D26,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F26" s="22" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="22" t="inlineStr">
+        <is>
+          <t>Ledger copy CUMVOUCH_BK240824 (CV_04a) to 31 Dec 2023 against the GL opening balances of 1 Jan 2024 (CV_14), 4 loan GLs: sum of the differences</t>
+        </is>
+      </c>
+      <c r="B27" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C27" s="25" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="D27" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E27" s="26">
+        <f>IF(ABS(B27-C27)&lt;=D27,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F27" s="22" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="22" t="inlineStr">
+        <is>
+          <t>Loan book 2025-12, MAIIC's loan GLs: carrying amount</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (book_2025-12_maiic_amount)</t>
+        </is>
+      </c>
+      <c r="C28" s="25" t="n">
+        <v>14841212779.54</v>
+      </c>
+      <c r="D28" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E28" s="26">
+        <f>IF(B28=C28,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F28" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="22" t="inlineStr">
+        <is>
+          <t>Loan book 2025-12, MAIIC's loan GLs: rows</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (book_2025-12_maiic_loans)</t>
+        </is>
+      </c>
+      <c r="C29" s="25" t="n">
+        <v>123</v>
+      </c>
+      <c r="D29" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E29" s="26">
+        <f>IF(B29=C29,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F29" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="22" t="inlineStr">
+        <is>
+          <t>Loan book 2025-12, Mega Farm programme GLs: carrying amount</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (book_2025-12_megafarm_amount)</t>
+        </is>
+      </c>
+      <c r="C30" s="25" t="n">
+        <v>54498560819.6</v>
+      </c>
+      <c r="D30" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E30" s="26">
+        <f>IF(B30=C30,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F30" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="22" t="inlineStr">
+        <is>
+          <t>Loan book 2025-12, Mega Farm programme GLs: accounts with a balance</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (book_2025-12_megafarm_accounts)</t>
+        </is>
+      </c>
+      <c r="C31" s="25" t="n">
+        <v>3671</v>
+      </c>
+      <c r="D31" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E31" s="26">
+        <f>IF(B31=C31,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F31" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="22" t="inlineStr">
+        <is>
+          <t>Loan book 2026-09, MAIIC's loan GLs: carrying amount</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (book_2026-09_maiic_amount)</t>
+        </is>
+      </c>
+      <c r="C32" s="25" t="n">
+        <v>23189580235.43</v>
+      </c>
+      <c r="D32" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E32" s="26">
+        <f>IF(B32=C32,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F32" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="22" t="inlineStr">
+        <is>
+          <t>Loan book 2026-09, MAIIC's loan GLs: rows</t>
+        </is>
+      </c>
+      <c r="B33" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (book_2026-09_maiic_loans)</t>
+        </is>
+      </c>
+      <c r="C33" s="25" t="n">
+        <v>134</v>
+      </c>
+      <c r="D33" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E33" s="26">
+        <f>IF(B33=C33,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F33" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="22" t="inlineStr">
+        <is>
+          <t>Loan book 2026-09, Mega Farm programme GLs: carrying amount</t>
+        </is>
+      </c>
+      <c r="B34" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (book_2026-09_megafarm_amount)</t>
+        </is>
+      </c>
+      <c r="C34" s="25" t="n">
+        <v>56180761113.43</v>
+      </c>
+      <c r="D34" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E34" s="26">
+        <f>IF(B34=C34,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F34" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="22" t="inlineStr">
+        <is>
+          <t>Loan book 2026-09, Mega Farm programme GLs: accounts with a balance</t>
+        </is>
+      </c>
+      <c r="B35" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (book_2026-09_megafarm_accounts)</t>
+        </is>
+      </c>
+      <c r="C35" s="25" t="n">
+        <v>3618</v>
+      </c>
+      <c r="D35" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E35" s="26">
+        <f>IF(B35=C35,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F35" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="22" t="inlineStr">
+        <is>
+          <t>Ledger write-offs on MAIIC loans (WriteOffClassifier): postings</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ledger_writeoffs_postings)</t>
+        </is>
+      </c>
+      <c r="C36" s="25" t="n">
+        <v>22</v>
+      </c>
+      <c r="D36" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E36" s="26">
+        <f>IF(B36=C36,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F36" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="22" t="inlineStr">
+        <is>
+          <t>Ledger write-offs on MAIIC loans (WriteOffClassifier): amount</t>
+        </is>
+      </c>
+      <c r="B37" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ledger_writeoffs_amount)</t>
+        </is>
+      </c>
+      <c r="C37" s="25" t="n">
+        <v>60778466.86</v>
+      </c>
+      <c r="D37" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E37" s="26">
+        <f>IF(B37=C37,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F37" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="22" t="inlineStr">
+        <is>
+          <t>ECL 2025-12, MAIIC's book: undiscounted</t>
+        </is>
+      </c>
+      <c r="B38" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ecl_2025-12_maiic_undiscounted)</t>
+        </is>
+      </c>
+      <c r="C38" s="25" t="n">
+        <v>3955543846.37</v>
+      </c>
+      <c r="D38" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E38" s="26">
+        <f>IF(B38=C38,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F38" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="22" t="inlineStr">
+        <is>
+          <t>ECL 2025-12, MAIIC's book: discounted at the EIR (booked)</t>
+        </is>
+      </c>
+      <c r="B39" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ecl_2025-12_maiic_discounted)</t>
+        </is>
+      </c>
+      <c r="C39" s="25" t="n">
+        <v>2593174242.3</v>
+      </c>
+      <c r="D39" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E39" s="26">
+        <f>IF(B39=C39,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F39" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="22" t="inlineStr">
+        <is>
+          <t>ECL 2025-12, MAIIC's book: loans discounted at the EIR</t>
+        </is>
+      </c>
+      <c r="B40" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ecl_2025-12_maiic_discounted_loans)</t>
+        </is>
+      </c>
+      <c r="C40" s="25" t="n">
+        <v>56</v>
+      </c>
+      <c r="D40" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E40" s="26">
+        <f>IF(B40=C40,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F40" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="22" t="inlineStr">
+        <is>
+          <t>ECL 2025-12, MAIIC's book, stage 1: discounted</t>
+        </is>
+      </c>
+      <c r="B41" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ecl_2025-12_maiic_stage1_discounted)</t>
+        </is>
+      </c>
+      <c r="C41" s="25" t="n">
+        <v>61318291.61</v>
+      </c>
+      <c r="D41" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E41" s="26">
+        <f>IF(B41=C41,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F41" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="22" t="inlineStr">
+        <is>
+          <t>ECL 2025-12, MAIIC's book, stage 2: discounted</t>
+        </is>
+      </c>
+      <c r="B42" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ecl_2025-12_maiic_stage2_discounted)</t>
+        </is>
+      </c>
+      <c r="C42" s="25" t="n">
+        <v>315409106.41</v>
+      </c>
+      <c r="D42" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E42" s="26">
+        <f>IF(B42=C42,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F42" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="22" t="inlineStr">
+        <is>
+          <t>ECL 2025-12, MAIIC's book, stage 3: discounted</t>
+        </is>
+      </c>
+      <c r="B43" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ecl_2025-12_maiic_stage3_discounted)</t>
+        </is>
+      </c>
+      <c r="C43" s="25" t="n">
+        <v>2216446844.28</v>
+      </c>
+      <c r="D43" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E43" s="26">
+        <f>IF(B43=C43,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F43" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="22" t="inlineStr">
+        <is>
+          <t>ECL 2025-12, Mega Farm programme (latest run)</t>
+        </is>
+      </c>
+      <c r="B44" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ecl_2025-12_megafarm_programme)</t>
+        </is>
+      </c>
+      <c r="C44" s="22" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="D44" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E44" s="26">
+        <f>IF(B44=C44,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F44" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="22" t="inlineStr">
+        <is>
+          <t>ECL 2025-12, Mega Farm: MAIIC's share</t>
+        </is>
+      </c>
+      <c r="B45" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ecl_2025-12_megafarm_maiic_share)</t>
+        </is>
+      </c>
+      <c r="C45" s="22" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="D45" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E45" s="26">
+        <f>IF(B45=C45,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F45" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="22" t="inlineStr">
+        <is>
+          <t>ECL 2026-09, MAIIC's book: undiscounted</t>
+        </is>
+      </c>
+      <c r="B46" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ecl_2026-09_maiic_undiscounted)</t>
+        </is>
+      </c>
+      <c r="C46" s="25" t="n">
+        <v>11569458915.88</v>
+      </c>
+      <c r="D46" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E46" s="26">
+        <f>IF(B46=C46,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F46" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="22" t="inlineStr">
+        <is>
+          <t>ECL 2026-09, MAIIC's book: discounted at the EIR (booked)</t>
+        </is>
+      </c>
+      <c r="B47" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ecl_2026-09_maiic_discounted)</t>
+        </is>
+      </c>
+      <c r="C47" s="25" t="n">
+        <v>7118643553.12</v>
+      </c>
+      <c r="D47" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E47" s="26">
+        <f>IF(B47=C47,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F47" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="22" t="inlineStr">
+        <is>
+          <t>ECL 2026-09, MAIIC's book: loans discounted at the EIR</t>
+        </is>
+      </c>
+      <c r="B48" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ecl_2026-09_maiic_discounted_loans)</t>
+        </is>
+      </c>
+      <c r="C48" s="25" t="n">
+        <v>62</v>
+      </c>
+      <c r="D48" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E48" s="26">
+        <f>IF(B48=C48,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F48" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="22" t="inlineStr">
+        <is>
+          <t>ECL 2026-09, MAIIC's book, stage 1: discounted</t>
+        </is>
+      </c>
+      <c r="B49" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ecl_2026-09_maiic_stage1_discounted)</t>
+        </is>
+      </c>
+      <c r="C49" s="25" t="n">
+        <v>219546033.9</v>
+      </c>
+      <c r="D49" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E49" s="26">
+        <f>IF(B49=C49,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F49" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="22" t="inlineStr">
+        <is>
+          <t>ECL 2026-09, MAIIC's book, stage 2: discounted</t>
+        </is>
+      </c>
+      <c r="B50" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ecl_2026-09_maiic_stage2_discounted)</t>
+        </is>
+      </c>
+      <c r="C50" s="25" t="n">
+        <v>183786390.69</v>
+      </c>
+      <c r="D50" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E50" s="26">
+        <f>IF(B50=C50,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F50" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="22" t="inlineStr">
+        <is>
+          <t>ECL 2026-09, MAIIC's book, stage 3: discounted</t>
+        </is>
+      </c>
+      <c r="B51" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ecl_2026-09_maiic_stage3_discounted)</t>
+        </is>
+      </c>
+      <c r="C51" s="25" t="n">
+        <v>6715311128.53</v>
+      </c>
+      <c r="D51" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E51" s="26">
+        <f>IF(B51=C51,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F51" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="22" t="inlineStr">
+        <is>
+          <t>ECL 2026-09, Mega Farm programme (latest run)</t>
+        </is>
+      </c>
+      <c r="B52" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ecl_2026-09_megafarm_programme)</t>
+        </is>
+      </c>
+      <c r="C52" s="25" t="n">
+        <v>45782301503.37</v>
+      </c>
+      <c r="D52" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E52" s="26">
+        <f>IF(B52=C52,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F52" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="22" t="inlineStr">
+        <is>
+          <t>ECL 2026-09, Mega Farm: MAIIC's share</t>
+        </is>
+      </c>
+      <c r="B53" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (ecl_2026-09_megafarm_maiic_share)</t>
+        </is>
+      </c>
+      <c r="C53" s="25" t="n">
+        <v>2289115075.17</v>
+      </c>
+      <c r="D53" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E53" s="26">
+        <f>IF(B53=C53,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F53" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="22" t="inlineStr">
+        <is>
+          <t>EIR contracts locked</t>
+        </is>
+      </c>
+      <c r="B54" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (eir_contracts_locked)</t>
+        </is>
+      </c>
+      <c r="C54" s="25" t="n">
+        <v>14</v>
+      </c>
+      <c r="D54" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E54" s="26">
+        <f>IF(B54=C54,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F54" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="22" t="inlineStr">
+        <is>
+          <t>EIR contracts blocked</t>
+        </is>
+      </c>
+      <c r="B55" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (eir_contracts_blocked)</t>
+        </is>
+      </c>
+      <c r="C55" s="25" t="n">
+        <v>33</v>
+      </c>
+      <c r="D55" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E55" s="26">
+        <f>IF(B55=C55,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F55" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="22" t="inlineStr">
+        <is>
+          <t>EIR contracts solved (an EIR computed)</t>
+        </is>
+      </c>
+      <c r="B56" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (eir_contracts_solved)</t>
+        </is>
+      </c>
+      <c r="C56" s="25" t="n">
+        <v>14</v>
+      </c>
+      <c r="D56" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E56" s="26">
+        <f>IF(B56=C56,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F56" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="22" t="inlineStr">
+        <is>
+          <t>EIR contracts in the contract master</t>
+        </is>
+      </c>
+      <c r="B57" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (eir_contracts)</t>
+        </is>
+      </c>
+      <c r="C57" s="25" t="n">
+        <v>144</v>
+      </c>
+      <c r="D57" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E57" s="26">
+        <f>IF(B57=C57,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F57" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="22" t="inlineStr">
+        <is>
+          <t>Revenue 2024: EIR interest recognised</t>
+        </is>
+      </c>
+      <c r="B58" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (revenue_2024_eir_interest)</t>
+        </is>
+      </c>
+      <c r="C58" s="25" t="n">
+        <v>25532678.7</v>
+      </c>
+      <c r="D58" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E58" s="26">
+        <f>IF(B58=C58,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F58" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="22" t="inlineStr">
+        <is>
+          <t>Revenue 2024: cash received</t>
+        </is>
+      </c>
+      <c r="B59" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (revenue_2024_cash_received)</t>
+        </is>
+      </c>
+      <c r="C59" s="25" t="n">
+        <v>34200000</v>
+      </c>
+      <c r="D59" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E59" s="26">
+        <f>IF(B59=C59,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F59" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="22" t="inlineStr">
+        <is>
+          <t>Revenue 2024: roll-forward rows</t>
+        </is>
+      </c>
+      <c r="B60" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (revenue_2024_rows)</t>
+        </is>
+      </c>
+      <c r="C60" s="25" t="n">
+        <v>20</v>
+      </c>
+      <c r="D60" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E60" s="26">
+        <f>IF(B60=C60,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F60" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="22" t="inlineStr">
+        <is>
+          <t>Revenue 2025: EIR interest recognised</t>
+        </is>
+      </c>
+      <c r="B61" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (revenue_2025_eir_interest)</t>
+        </is>
+      </c>
+      <c r="C61" s="25" t="n">
+        <v>663970866.88</v>
+      </c>
+      <c r="D61" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E61" s="26">
+        <f>IF(B61=C61,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F61" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="22" t="inlineStr">
+        <is>
+          <t>Revenue 2025: cash received</t>
+        </is>
+      </c>
+      <c r="B62" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (revenue_2025_cash_received)</t>
+        </is>
+      </c>
+      <c r="C62" s="25" t="n">
+        <v>1158267060.2</v>
+      </c>
+      <c r="D62" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E62" s="26">
+        <f>IF(B62=C62,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F62" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="22" t="inlineStr">
+        <is>
+          <t>Revenue 2025: roll-forward rows</t>
+        </is>
+      </c>
+      <c r="B63" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (revenue_2025_rows)</t>
+        </is>
+      </c>
+      <c r="C63" s="25" t="n">
+        <v>126</v>
+      </c>
+      <c r="D63" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E63" s="26">
+        <f>IF(B63=C63,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F63" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="22" t="inlineStr">
+        <is>
+          <t>Revenue 2026: EIR interest recognised</t>
+        </is>
+      </c>
+      <c r="B64" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (revenue_2026_eir_interest)</t>
+        </is>
+      </c>
+      <c r="C64" s="25" t="n">
+        <v>544517024.26</v>
+      </c>
+      <c r="D64" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E64" s="26">
+        <f>IF(B64=C64,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F64" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="22" t="inlineStr">
+        <is>
+          <t>Revenue 2026: cash received</t>
+        </is>
+      </c>
+      <c r="B65" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (revenue_2026_cash_received)</t>
+        </is>
+      </c>
+      <c r="C65" s="25" t="n">
+        <v>2381610987.63</v>
+      </c>
+      <c r="D65" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E65" s="26">
+        <f>IF(B65=C65,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F65" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="22" t="inlineStr">
+        <is>
+          <t>Revenue 2026: roll-forward rows</t>
+        </is>
+      </c>
+      <c r="B66" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (revenue_2026_rows)</t>
+        </is>
+      </c>
+      <c r="C66" s="25" t="n">
+        <v>113</v>
+      </c>
+      <c r="D66" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E66" s="26">
+        <f>IF(B66=C66,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F66" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="22" t="inlineStr">
+        <is>
+          <t>RBM return 2026-09: facilities classified loss (paragraph 12 list)</t>
+        </is>
+      </c>
+      <c r="B67" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (rbm_2026-09_loss_facilities)</t>
+        </is>
+      </c>
+      <c r="C67" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="D67" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E67" s="26">
+        <f>IF(B67=C67,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F67" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="22" t="inlineStr">
+        <is>
+          <t>RBM return 2026-09: balance of the loss list</t>
+        </is>
+      </c>
+      <c r="B68" s="22" t="inlineStr">
+        <is>
+          <t>no golden value committed (rbm_2026-09_loss_balance)</t>
+        </is>
+      </c>
+      <c r="C68" s="25" t="n">
+        <v>1510956083.45</v>
+      </c>
+      <c r="D68" s="22" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E68" s="26">
+        <f>IF(B68=C68,"PASS","FAIL")</f>
+        <v/>
+      </c>
+      <c r="F68" s="22" t="inlineStr">
+        <is>
+          <t>the bootstrap's verify reports this row</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="E5:E14">
+  <conditionalFormatting sqref="E5:E68">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$E5="PASS"</formula>
     </cfRule>
